--- a/www/terminologies/ValueSet-jdv-specimen-type-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-specimen-type-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141838</t>
+    <t>20260220142104</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:38+01:00</t>
+    <t>2026-02-20T14:21:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-specimen-type-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-specimen-type-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142104</t>
+    <t>20260311144903</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:04+01:00</t>
+    <t>2026-03-11T14:49:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-specimen-type-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-specimen-type-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144903</t>
+    <t>20260420150250</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:03+01:00</t>
+    <t>2026-04-20T15:02:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-specimen-type-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-specimen-type-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150250</t>
+    <t>20260619134042</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:50+01:00</t>
+    <t>2026-06-19T13:40:42+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-specimen-type-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-specimen-type-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134042</t>
+    <t>20260420150250</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:42+01:00</t>
+    <t>2026-04-20T15:02:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-specimen-type-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-specimen-type-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134042</t>
+    <t>20260716085852</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:42+01:00</t>
+    <t>2026-07-16T08:58:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
